--- a/docs/PRAP_Development_Plan_v2.53.xlsx
+++ b/docs/PRAP_Development_Plan_v2.53.xlsx
@@ -7418,7 +7418,7 @@
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
-          <t>R-45, REQ-DSH-16: FIVE THINGS ABOUT READING THE SCREEN, all reported from the field, none of them a change to a figure. ONE. THE TWO UTILISATION CHARTS GROW WITH THE HORIZON. They were a fixed 1,080 wide whatever the span, which is right for the two years almost everybody opens on and wrong for the long plans that most need reading: five years is sixty columns in 790 points of plot, thirteen points each, and a three-letter month does not fit in thirteen points - so the axis ran its labels into one another exactly where the chart stopped being optional. Each month is now guaranteed 32 points and the panel scrolls sideways past the point where they all fit, which is what every other chart on the page already did. 32 rather than a rounder number so that at 24 months the chart is EXACTLY the width it has always been and this change is invisible to anyone who did not need it. TWO. ASSIGNMENTS, WEIGHT OVERRIDES AND MONTHLY ESTIMATION ARE ONE COLUMN, NOT TWO. They were a two-column grid, so each of three wide tables - eleven columns, seven and eight, one of those a sentence of arithmetic - had half a screen and all three scrolled sideways permanently. Stacked full width they also read in the order they are worked in: pick the assignment, then its override windows, then its months. THREE. MONTHLY ESTIMATION NAMES ITS ASSIGNMENT. It is a child of the row selected above it and said so nowhere - eight columns of months with no statement of what they belong to. It now carries the same line Weight overrides carries, word for word from one helper so the two cannot drift: the id, the project, the role, the window and the weight. FOUR. CLICKING A LEGEND ENTRY PICKS THAT SERIES OUT OF THE CHART. Twenty bands in twenty shades of one palette read perfectly well as a total and not at all as a series; finding one project in the stack by colour alone means carrying a swatch in your head down sixty months of bars. Everything that is not the picked series fades back; a second click, another entry, or Escape brings it home. THE PICK APPLIES TO THE WHOLE TAB, because the question is 'where is this project on this page' and not 'where is it in this one drawing' - the trend line, the stack and the timeline all mean the same project by the same id, so one click answers it in all three. A CHART CUT ALONG A DIFFERENT AXIS IS LEFT ALONE: a person's id means nothing to a chart stacked by project, and dimming it anyway would fade a whole chart to nothing and light none of it, which reads as 'this has no data' rather than 'you asked something this chart cannot answer'. A timeline band is a period OF a project and carries both keys, so picking a period lights it across every project and picking a project lights that project's whole row. Marks belonging to the MONTH rather than to any series - the threshold lines, the baseline, the outline that marks a month off its standard - never fade. Every entry is a real button: focusable, operable from the keyboard, and it states whether it is pressed (D-04). FIVE. EVERY HEADING SAYS WHAT THE COLUMN MEANS. The tables have always shown the workbook's own column names and that is right - the screen and the file are the same thing, so a name on screen is one you can find in the spreadsheet, quote in a mail or search the specification for. It is also, on its own, a poor label: work_scope_type, outsourcing_scope_det, absorbed_by and ref_id are legible to whoever wrote the schema and opaque to the person filling the plan in, and the meaning was only ever a hover away, which is to say invisible to anyone who did not know to hover. Each heading now carries BOTH lines - the plain name first, in the page's own type, and the column name under it in the monospace this application uses for every other identifier. NOTHING IS RENAMED: the file keeps its columns, every validation message still names them, and the cell still writes back through the identifier. The same head is used on the heading's pop-up, on every cell's and on the filter buttons', so it is learned once. No calculation change, no schema change and no figure moves. tools/test_screen.py and tools/test_labels.py are new, 33 checks between them; test_columns and test_lookup read the identifier from the heading's second line.</t>
+          <t>R-45, REQ-DSH-16: FIVE THINGS ABOUT READING THE SCREEN, all reported from the field, none of them a change to a figure. ONE. THE TWO UTILISATION CHARTS GROW WITH THE HORIZON. They were a fixed 1,080 wide whatever the span, which is right for the two years almost everybody opens on and wrong for the long plans that most need reading: five years is sixty columns in 790 points of plot, thirteen points each, and a three-letter month does not fit in thirteen points - so the axis ran its labels into one another exactly where the chart stopped being optional. Each month is now guaranteed 32 points and the panel scrolls sideways past the point where they all fit, which is what every other chart on the page already did. 32 rather than a rounder number so that at 24 months the chart is EXACTLY the width it has always been and this change is invisible to anyone who did not need it. TWO. ASSIGNMENTS, WEIGHT OVERRIDES AND MONTHLY ESTIMATION ARE ONE COLUMN, NOT TWO. They were a two-column grid, so each of three wide tables - eleven columns, seven and eight, one of those a sentence of arithmetic - had half a screen and all three scrolled sideways permanently. Stacked full width they also read in the order they are worked in: pick the assignment, then its override windows, then its months. THREE. MONTHLY ESTIMATION NAMES ITS ASSIGNMENT. It is a child of the row selected above it and said so nowhere - eight columns of months with no statement of what they belong to. It now carries the same line Weight overrides carries, word for word from one helper so the two cannot drift: the id, the project, the role, the window and the weight. FOUR. CLICKING A LEGEND ENTRY PICKS THAT SERIES OUT OF THE CHART. Twenty bands in twenty shades of one palette read perfectly well as a total and not at all as a series; finding one project in the stack by colour alone means carrying a swatch in your head down sixty months of bars. Everything that is not the picked series fades back; a second click, another entry, or Escape brings it home. THE PICK APPLIES TO THE WHOLE TAB, because the question is 'where is this project on this page' and not 'where is it in this one drawing' - the trend line, the stack and the timeline all mean the same project by the same id, so one click answers it in all three. A CHART CUT ALONG A DIFFERENT AXIS IS LEFT ALONE: a person's id means nothing to a chart stacked by project, and dimming it anyway would fade a whole chart to nothing and light none of it, which reads as 'this has no data' rather than 'you asked something this chart cannot answer'. A timeline band is a period OF a project and carries both keys, so picking a period lights it across every project and picking a project lights that project's whole row. Marks belonging to the MONTH rather than to any series - the threshold lines, the baseline, the outline that marks a month off its standard - never fade. Every entry is a real button: focusable, operable from the keyboard, and it states whether it is pressed (D-04). FIVE. EVERY HEADING SAYS WHAT THE COLUMN MEANS. The tables have always shown the workbook's own column names and that is right - the screen and the file are the same thing, so a name on screen is one you can find in the spreadsheet, quote in a mail or search the specification for. It is also, on its own, a poor label: work_scope_type, outsourcing_scope_det, absorbed_by and ref_id are legible to whoever wrote the schema and opaque to the person filling the plan in, and the meaning was only ever a hover away, which is to say invisible to anyone who did not know to hover. Each heading now carries BOTH lines - the plain name first, in the page's own type, and the column name under it in the monospace this application uses for every other identifier. NOTHING IS RENAMED: the file keeps its columns, every validation message still names them, and the cell still writes back through the identifier. The same head is used on the heading's pop-up, on every cell's and on the filter buttons', so it is learned once. ONE DEFECT EXPOSED, NOT CAUSED, AND FIXED. Widening those three panels put a table into a gap no layout before it had landed in: the two drawn scroll bars decide each other, each costing the region 15px of its own space, and paintCue measured once - so a region that only overflows sideways ONCE ITS OWN VERTICAL BAR IS DRAWN got no horizontal bar, which is exactly the failure REQ-DSH-13 exists to prevent. Measured on the 62-project fixture: scrollWidth 1316 with both flags off and 1318 with the vertical bar there, against a client width of 1316 - two pixels, which is why no earlier layout met it. The flags are now settled before anything is drawn, and it cannot oscillate because padding can only create overflow, never remove it. Found by the REQ-DSH-13 check in test_ui, which failed on this build and passes on the fix. No calculation change, no schema change and no figure moves. tools/test_screen.py and tools/test_labels.py are new, 33 checks between them; test_columns and test_lookup read the identifier from the heading's second line.</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">

--- a/docs/PRAP_Development_Plan_v2.53.xlsx
+++ b/docs/PRAP_Development_Plan_v2.53.xlsx
@@ -7418,7 +7418,7 @@
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
-          <t>R-45, REQ-DSH-16: FIVE THINGS ABOUT READING THE SCREEN, all reported from the field, none of them a change to a figure. ONE. THE TWO UTILISATION CHARTS GROW WITH THE HORIZON. They were a fixed 1,080 wide whatever the span, which is right for the two years almost everybody opens on and wrong for the long plans that most need reading: five years is sixty columns in 790 points of plot, thirteen points each, and a three-letter month does not fit in thirteen points - so the axis ran its labels into one another exactly where the chart stopped being optional. Each month is now guaranteed 32 points and the panel scrolls sideways past the point where they all fit, which is what every other chart on the page already did. 32 rather than a rounder number so that at 24 months the chart is EXACTLY the width it has always been and this change is invisible to anyone who did not need it. TWO. ASSIGNMENTS, WEIGHT OVERRIDES AND MONTHLY ESTIMATION ARE ONE COLUMN, NOT TWO. They were a two-column grid, so each of three wide tables - eleven columns, seven and eight, one of those a sentence of arithmetic - had half a screen and all three scrolled sideways permanently. Stacked full width they also read in the order they are worked in: pick the assignment, then its override windows, then its months. THREE. MONTHLY ESTIMATION NAMES ITS ASSIGNMENT. It is a child of the row selected above it and said so nowhere - eight columns of months with no statement of what they belong to. It now carries the same line Weight overrides carries, word for word from one helper so the two cannot drift: the id, the project, the role, the window and the weight. FOUR. CLICKING A LEGEND ENTRY PICKS THAT SERIES OUT OF THE CHART. Twenty bands in twenty shades of one palette read perfectly well as a total and not at all as a series; finding one project in the stack by colour alone means carrying a swatch in your head down sixty months of bars. Everything that is not the picked series fades back; a second click, another entry, or Escape brings it home. THE PICK APPLIES TO THE WHOLE TAB, because the question is 'where is this project on this page' and not 'where is it in this one drawing' - the trend line, the stack and the timeline all mean the same project by the same id, so one click answers it in all three. A CHART CUT ALONG A DIFFERENT AXIS IS LEFT ALONE: a person's id means nothing to a chart stacked by project, and dimming it anyway would fade a whole chart to nothing and light none of it, which reads as 'this has no data' rather than 'you asked something this chart cannot answer'. A timeline band is a period OF a project and carries both keys, so picking a period lights it across every project and picking a project lights that project's whole row. Marks belonging to the MONTH rather than to any series - the threshold lines, the baseline, the outline that marks a month off its standard - never fade. Every entry is a real button: focusable, operable from the keyboard, and it states whether it is pressed (D-04). FIVE. EVERY HEADING SAYS WHAT THE COLUMN MEANS. The tables have always shown the workbook's own column names and that is right - the screen and the file are the same thing, so a name on screen is one you can find in the spreadsheet, quote in a mail or search the specification for. It is also, on its own, a poor label: work_scope_type, outsourcing_scope_det, absorbed_by and ref_id are legible to whoever wrote the schema and opaque to the person filling the plan in, and the meaning was only ever a hover away, which is to say invisible to anyone who did not know to hover. Each heading now carries BOTH lines - the plain name first, in the page's own type, and the column name under it in the monospace this application uses for every other identifier. NOTHING IS RENAMED: the file keeps its columns, every validation message still names them, and the cell still writes back through the identifier. The same head is used on the heading's pop-up, on every cell's and on the filter buttons', so it is learned once. ONE DEFECT EXPOSED, NOT CAUSED, AND FIXED. Widening those three panels put a table into a gap no layout before it had landed in: the two drawn scroll bars decide each other, each costing the region 15px of its own space, and paintCue measured once - so a region that only overflows sideways ONCE ITS OWN VERTICAL BAR IS DRAWN got no horizontal bar, which is exactly the failure REQ-DSH-13 exists to prevent. Measured on the 62-project fixture: scrollWidth 1316 with both flags off and 1318 with the vertical bar there, against a client width of 1316 - two pixels, which is why no earlier layout met it. The flags are now settled before anything is drawn, and it cannot oscillate because padding can only create overflow, never remove it. Found by the REQ-DSH-13 check in test_ui, which failed on this build and passes on the fix. No calculation change, no schema change and no figure moves. tools/test_screen.py and tools/test_labels.py are new, 33 checks between them; test_columns and test_lookup read the identifier from the heading's second line.</t>
+          <t>R-45, REQ-DSH-16: FIVE THINGS ABOUT READING THE SCREEN, all reported from the field, none of them a change to a figure. ONE. THE TWO UTILISATION CHARTS GROW WITH THE HORIZON. They were a fixed 1,080 wide whatever the span, which is right for the two years almost everybody opens on and wrong for the long plans that most need reading: five years is sixty columns in 790 points of plot, thirteen points each, and a three-letter month does not fit in thirteen points - so the axis ran its labels into one another exactly where the chart stopped being optional. Each month is now guaranteed 32 points and the panel scrolls sideways past the point where they all fit, which is what every other chart on the page already did. 32 rather than a rounder number so that at 24 months the chart is EXACTLY the width it has always been and this change is invisible to anyone who did not need it. TWO. ASSIGNMENTS, WEIGHT OVERRIDES AND MONTHLY ESTIMATION ARE ONE COLUMN, NOT TWO. They were a two-column grid, so each of three wide tables - eleven columns, seven and eight, one of those a sentence of arithmetic - had half a screen and all three scrolled sideways permanently. Stacked full width they also read in the order they are worked in: pick the assignment, then its override windows, then its months. THREE. MONTHLY ESTIMATION NAMES ITS ASSIGNMENT. It is a child of the row selected above it and said so nowhere - eight columns of months with no statement of what they belong to. It now carries the same line Weight overrides carries, word for word from one helper so the two cannot drift: the id, the project, the role, the window and the weight. FOUR. CLICKING A LEGEND ENTRY PICKS THAT SERIES OUT OF THE CHART. Twenty bands in twenty shades of one palette read perfectly well as a total and not at all as a series; finding one project in the stack by colour alone means carrying a swatch in your head down sixty months of bars. Everything that is not the picked series fades back; a second click, another entry, or Escape brings it home. THE PICK APPLIES TO THE WHOLE TAB, because the question is 'where is this project on this page' and not 'where is it in this one drawing' - the trend line, the stack and the timeline all mean the same project by the same id, so one click answers it in all three. A CHART CUT ALONG A DIFFERENT AXIS IS LEFT ALONE: a person's id means nothing to a chart stacked by project, and dimming it anyway would fade a whole chart to nothing and light none of it, which reads as 'this has no data' rather than 'you asked something this chart cannot answer'. A timeline band is a period OF a project and carries both keys, so picking a period lights it across every project and picking a project lights that project's whole row. Marks belonging to the MONTH rather than to any series - the threshold lines, the baseline, the outline that marks a month off its standard - never fade. Every entry is a real button: focusable, operable from the keyboard, and it states whether it is pressed (D-04). FIVE. EVERY HEADING SAYS WHAT THE COLUMN MEANS, AND ONLY THAT. The tables used to show the workbook's own column names: work_scope_type, outsourcing_scope_det, absorbed_by, ref_id - legible to whoever wrote the schema and opaque to the person filling the plan in. The meaning was only ever a hover away, which is to say invisible to anyone who did not know to hover. The heading now prints the plain name and nothing else. THE COLUMN'S OWN NAME IS IN THE POP-UP, NOT ON THE PAGE, and this was decided twice. It was first put on a second line under the label, on the reasoning that the screen and the file are the same thing, so a heading you cannot find in the spreadsheet is one you cannot quote in a mail or look up in a document. That reasoning was right about the NEED and wrong about the PLACE, which the reviewer said plainly: the need is occasional - you go looking for a column name when you are editing the workbook or chasing a finding - and the heading is read on every glance by everyone. Paying for a rare need out of the common one is the wrong way round when the pop-up already answers it in full. Every heading now carries a pop-up naming both, and the identifier is on the element as data-cid for whatever needs to read it. The badge on a derived column names the plain name too - a heading row that has stopped printing identifiers must not keep one in a badge. NOTHING IS RENAMED: the file keeps its columns, every validation message still names them, and the cell still writes back through the identifier. The same head is used on the heading's pop-up, on every cell's and on the filter buttons', so it is learned once. ONE DEFECT EXPOSED, NOT CAUSED, AND FIXED. Widening those three panels put a table into a gap no layout before it had landed in: the two drawn scroll bars decide each other, each costing the region 15px of its own space, and paintCue measured once - so a region that only overflows sideways ONCE ITS OWN VERTICAL BAR IS DRAWN got no horizontal bar, which is exactly the failure REQ-DSH-13 exists to prevent. Measured on the 62-project fixture: scrollWidth 1316 with both flags off and 1318 with the vertical bar there, against a client width of 1316 - two pixels, which is why no earlier layout met it. The flags are now settled before anything is drawn, and it cannot oscillate because padding can only create overflow, never remove it. Found by the REQ-DSH-13 check in test_ui, which failed on this build and passes on the fix. No calculation change, no schema change and no figure moves. tools/test_screen.py and tools/test_labels.py are new, 33 checks between them; test_columns and test_lookup read the identifier from the heading's second line.</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>THE SCREEN IS READABLE AT THE SIZE THE PLAN ACTUALLY IS, AND SAYS WHAT ITS COLUMNS MEAN. Five things, none of which changes a figure. (a) A CHART THAT CAN RUN LONG GROWS WITH ITS HORIZON AND ITS PANEL SCROLLS. Every month is guaranteed a minimum width of plot; past the point where they all fit, the panel scrolls sideways rather than compressing the axis until its labels overlap. A fixed width is only readable over the span it was chosen for, and it fails silently - the chart still draws, it simply stops being legible, and it does so on the long plans that most need reading. The default two-year view is unchanged, so the rule is invisible to anyone who did not need it. (b) A WIDE TABLE GETS THE WHOLE WIDTH. Panels are placed side by side only where both are narrow enough to be read there; three tables of eleven, seven and eight columns are stacked, in the order the work is done in - the assignment, then its override windows, then its months - not tiled into halves that each scroll sideways permanently. (c) A PANEL THAT IS A CHILD OF A SELECTION NAMES THE ROW IT BELONGS TO, under its title, from ONE helper shared with every other panel that names the same thing, so two statements of the same fact cannot drift apart. (d) CLICKING A LEGEND ENTRY PICKS THAT SERIES OUT: everything that is not it fades back, a second click or Escape brings it home. Twenty bands in twenty shades of one palette read as a total and not as a series, and the fix is not more colours. THE PICK APPLIES TO THE WHOLE TAB, because the question asked is 'where is this project on this page'; a chart cut along a DIFFERENT axis, which has no mark for that key at all, is left alone rather than faded to nothing, since a chart with everything dimmed and nothing lit reads as 'this has no data' instead of 'this cannot answer that'. A mark standing for two series at once - a timeline band is a period OF a project - answers to either. Marks belonging to the MONTH rather than to a series never fade: thresholds, baselines, and the outline that marks a month off its standard are facts about the month and stay at full strength. Every entry is a button, operable from the keyboard and stating whether it is pressed (D-04). (e) EVERY COLUMN HEADING CARRIES A PLAIN NAME AND THE COLUMN'S OWN NAME, in that order. The workbook's column names must stay on screen - the screen and the file are the same thing, so a heading is something to find in the spreadsheet, quote in a mail and look up in this document - and they are not, by themselves, labels: the meaning existed only in a pop-up, which is to say only for a reader who knew to hover. Both lines are shown, nothing is renamed, the cell still writes back through the identifier, and the same two-part head is used on the heading's pop-up, on every cell's and on the filter buttons', so it is learned once.</t>
+          <t>THE SCREEN IS READABLE AT THE SIZE THE PLAN ACTUALLY IS, AND SAYS WHAT ITS COLUMNS MEAN. Five things, none of which changes a figure. (a) A CHART THAT CAN RUN LONG GROWS WITH ITS HORIZON AND ITS PANEL SCROLLS. Every month is guaranteed a minimum width of plot; past the point where they all fit, the panel scrolls sideways rather than compressing the axis until its labels overlap. A fixed width is only readable over the span it was chosen for, and it fails silently - the chart still draws, it simply stops being legible, and it does so on the long plans that most need reading. The default two-year view is unchanged, so the rule is invisible to anyone who did not need it. (b) A WIDE TABLE GETS THE WHOLE WIDTH. Panels are placed side by side only where both are narrow enough to be read there; three tables of eleven, seven and eight columns are stacked, in the order the work is done in - the assignment, then its override windows, then its months - not tiled into halves that each scroll sideways permanently. (c) A PANEL THAT IS A CHILD OF A SELECTION NAMES THE ROW IT BELONGS TO, under its title, from ONE helper shared with every other panel that names the same thing, so two statements of the same fact cannot drift apart. (d) CLICKING A LEGEND ENTRY PICKS THAT SERIES OUT: everything that is not it fades back, a second click or Escape brings it home. Twenty bands in twenty shades of one palette read as a total and not as a series, and the fix is not more colours. THE PICK APPLIES TO THE WHOLE TAB, because the question asked is 'where is this project on this page'; a chart cut along a DIFFERENT axis, which has no mark for that key at all, is left alone rather than faded to nothing, since a chart with everything dimmed and nothing lit reads as 'this has no data' instead of 'this cannot answer that'. A mark standing for two series at once - a timeline band is a period OF a project - answers to either. Marks belonging to the MONTH rather than to a series never fade: thresholds, baselines, and the outline that marks a month off its standard are facts about the month and stay at full strength. Every entry is a button, operable from the keyboard and stating whether it is pressed (D-04). (e) EVERY COLUMN HEADING IS A PLAIN NAME, and the workbook's own column name is in the pop-up rather than on the page. Those column names are not, by themselves, labels, and their meaning existed only in a pop-up - which is to say only for a reader who knew to hover. WHERE THE IDENTIFIER BELONGS WAS SETTLED TWICE and the second answer is the one to keep: it was first printed on a second line under the label, because the screen and the file are the same thing and a heading must be findable in the spreadsheet; but looking a column name up is OCCASIONAL - editing the workbook, chasing a finding - while a heading is read on EVERY glance, so printing it charged the common case for the rare one when the pop-up already answered it in full. Every heading carries a pop-up naming both, and the identifier as data-cid for whatever must read it. Nothing is renamed, the cell still writes back through the identifier, and the same two-part head is used on the heading's pop-up, on every cell's and on the filter buttons', so it is learned once.</t>
         </is>
       </c>
       <c r="D32" s="17" t="inlineStr">
